--- a/mosip_master/xlsx/template.xlsx
+++ b/mosip_master/xlsx/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nira-registration\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F94682-2325-4710-BCCC-954FE79E9E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8684C12B-95B2-42BA-AC14-985B73E3E5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5450,660 +5450,6 @@
   </si>
   <si>
     <t>Preview generated after registration COP</t>
-  </si>
-  <si>
-    <t>&lt;!DOCTYPE html&gt;
-&lt;html $rtl&gt;
-&lt;head&gt;
-    &lt;style&gt;
-        body {
-            font-family: "Roboto";
-        }
-        table,
-        .head {
-            font-size: 13px;
-        }
-        .demoDiv {
-            width: 85%;
-            float: left;
-            padding: 1.5px;
-        }
-        .photoDiv {
-            width: 15%;
-            float: right;
-        }
-        .form {
-            display: inline-block;
-        }
-        .section {
-            align: center;
-            padding: 30px;
-            width: 800px;
-            margin: auto;
-        }
-        .headings {
-            color: #808080;
-            font-size: 12px;
-        }
-        p {
-            display: inline;
-        }
-        .dataTable {
-            word-wrap: break-word;
-            table-layout: fixed;
-            width: 70%;
-        }
-        .headerTable {
-            width: 90%;
-        }
-        .NINHeaderTable {
-            width: 100%;
-        }
-        h5 {
-            display: inline;
-            position: absolute;
-        }
-        .iris {
-            top: -15px;
-            left: 152px;
-        }
-        .irisWithoutException {
-            top: -15px;
-            left: 114px;
-        }
-        .tableWithoutException {
-            width: 50%;
-            text-align: center;
-            table-layout: fixed;
-            margin: 0 auto;
-        }
-        .biometricsTable {
-            width: 100%;
-            text-align: center;
-            table-layout: fixed;
-        }
-        .biometrics {
-            position: relative;
-        }
-        .leftLittle {
-            top: 15px;
-            left: 11px;
-            display: inline;
-            position: absolute;
-        }
-        .leftRing {
-            top: 3px;
-            left: 23px;
-        }
-        .leftMiddle {
-            top: -7px;
-            left: 37px;
-        }
-        .leftIndex {
-            top: 3px;
-            left: 54px;
-        }
-        .rightIndex {
-            top: 3px;
-            left: 26px;
-        }
-        .rightMiddle {
-            top: -7px;
-            left: 39px;
-        }
-        .rightRing {
-            top: 3px;
-            left: 55px;
-        }
-        .rightLittle {
-            top: 15px;
-            left: 68px;
-        }
-        .leftThumb {
-            top: -4px;
-            left: 24px;
-        }
-        .rightThumb {
-            top: -4px;
-            left: 54px;
-        }
-        .parentStyle {
-            top: -15px;
-            left: 152px;
-        }
-        .parentIris1 {
-            top: -15px;
-            left: 212px;
-        }
-        .parentIris2 {
-            top: -15px;
-            left: 214px;
-        }
-        li span {
-            color: black;
-            font-size: 12px;
-        }
-        li {
-            color: #808080;
-        }
-        button {
-            float: right;
-            font-size: 12px;
-            border: none;
-            background-color: transparent;
-            outline: none;
-        }
-        button:active {
-            background-color: black;
-            color: white;
-        }
-        .bottom {
-            vertical-align: bottom;
-        }
-        .consent-block {
-            font-size: 13px;
-            border-radius: 8px;
-            margin-top: 10px;
-            margin-bottom: 10px;
-            border: 2px solid #E88E3F;
-            padding-top: -50px;
-            padding: 10px;
-        }
-        .consent-text {
-            margin-left: 7px;
-            margin-bottom: 4px;
-        }
-        input[type="radio"] {
-            display: none;
-        }
-        input[type="radio"]+label:before {
-            content: "";
-            display: inline-block;
-            width: 15px;
-            height: 15px;
-            padding: 3px;
-            margin-right: 5px;
-            background-clip: content-box;
-            /* border: 1px solid grey; */
-            background-color: #fff;
-            border-radius: 50%;
-        }
-        input[type="radio"]:checked+label:before {
-            background-color: #FF4081;
-            border-color: #FF4081;
-        }
-        *,
-        *:before,
-        *:after {
-            box-sizing: border-box;
-        }
-        .consent-block label {
-            display: inline-flex;
-            align-items: center;
-        }
-        /* .demoDiv&gt;table {
-            width: 100%
-        } */
-        /* .demoDiv&gt;table&gt;tbody&gt;tr&gt;th {
-            color: #808080;
-            font-size: 10px;
-            width: 25%;
-            text-align: left;
-            padding: 1.5px;
-        }
-        .demoDiv&gt;table&gt;tbody&gt;tr&gt;td {
-            font-size: 12px;
-            width: 25%;
-            text-align: left;
-            padding: 2px;
-        } */
-        ol {
-            font-size: 12px;
-        }
-    &lt;/style&gt;
-    &lt;script&gt;function changeColour(element) { var div = document.getElementById("radioId"); if (element.value == "yes") { div.style = "border: 2px solid #68A933"; } if (element.value == "no") { div.style = "border: 2px solid #FF0000"; } } document.onreadystatechange = function () { if (document.readyState === "complete") { var body = document.getElementsByTagName("body")[0]; body.addEventListener("dragstart", function (event) { event.preventDefault(); }); body.addEventListener("selectstart", function (event) { event.preventDefault(); }); } }&lt;/script&gt;
-&lt;/head&gt;
-&lt;body&gt;
-    &lt;div class=section&gt;
-        &lt;div class=form&gt;
-            &lt;table class=headerTable&gt;
-                &lt;tr&gt;
-                    &lt;td class=bottom&gt;
-                        &lt;p class=headings&gt;${ApplicationIDLabel}&lt;/p&gt;
-                        &lt;br /&gt;${ApplicationID}
-                    &lt;/td&gt;
-                    &lt;td class=bottom&gt;
-                        &lt;p class=headings&gt;${DateLabel}&lt;/p&gt;
-                        &lt;br /&gt;${Date}
-                    &lt;/td&gt;
-                &lt;/tr&gt;
-            &lt;/table&gt;
-            &lt;br /&gt; #if ( $name )
-            &lt;table class=headerTable&gt;
-                &lt;tr&gt;
-                    &lt;td&gt;
-                        &lt;p class=headings&gt;${NameLabel}&lt;/p&gt;
-                        &lt;br /&gt;${NameValue}
-                    &lt;/td&gt;
-                &lt;/tr&gt;
-            &lt;/table&gt;
-            #end &lt;br /&gt;
-            &lt;hr /&gt;
-            &lt;p class="head"&gt;&lt;b&gt;${DemographicInfo}&lt;/b&gt;&lt;/p&gt;
-            &lt;hr /&gt;
-            &lt;table class="demoDiv" style="width: 85%; border-spacing: 10px;"&gt;
-                &lt;tr&gt;
-                    #set( $counter = 0 )
-                    #set( $orderedFields = [ "surnameCop",
-                    "givenNameCop",
-                    "otherNamesCop",
-                    "genderCop",
-                    "dateOfBirthCop",
-                    "NIN",
-                    "email",
-                    "CountryCode",
-                    "phone",
-                    "homePhoneNumber",
-                    "nameOfNextOfKin",
-                    "telephoneNumberOfNextOfKin",
-                    "emailOfNextOfKin"
-                     ] ) &lt;!-- Define the order of fields --&gt;
-                &lt;tr&gt; &lt;!-- Start the first row --&gt;
-                    #foreach( $field in $orderedFields )
-                       #if( $demographics.containsKey($field) &amp;&amp; $demographics.get($field).get("value") )
-                    &lt;!-- Check if the field exists and has a value --&gt;
-                    &lt;td style="vertical-align: top; width: 28%;"&gt;
-                        &lt;p class="headings"&gt;&lt;b&gt;$demographics.get($field).get("label")&lt;/b&gt;&lt;/p&gt;&lt;br /&gt;
-                        &lt;p&gt;$demographics.get($field).get("value")&lt;/p&gt;
-                    &lt;/td&gt;
-                    #set( $counter = $counter + 1 )
-                    #if( $counter % 3 == 0 )
-                &lt;/tr&gt;
-                &lt;tr&gt; &lt;!-- Close current row and start a new one after 3 fields --&gt;
-                    #end
-                    #end
-                    #end
-                &lt;/tr&gt; &lt;!-- Close the last row --&gt;
-                &lt;/tr&gt;
-            &lt;/table&gt;
-            #if ( $ApplicantImageSource )
-            &lt;!-- &lt;div class="photoDiv" style="vertical-align: top; float: right;"&gt; --&gt;
-            &lt;table style="vertical-align: top; float: right;  width: 15%;"&gt;
-                &lt;tr&gt;
-                    &lt;td&gt;
-                        &lt;p&gt;${Photo}&lt;/p&gt;
-                    &lt;/td&gt;
-                &lt;/tr&gt;
-                &lt;tr&gt;
-                    &lt;td&gt;&lt;img src=${ApplicantImageSource} width=100 height=100 /&gt;&lt;/td&gt;
-                &lt;/tr&gt;
-            &lt;/table&gt;
-            #end
-            &lt;div style="width: 100%; height: 50%; clear:both"&gt;&lt;/div&gt;
-            &lt;br&gt; &lt;br /&gt;
-            &lt;hr /&gt;
-            &lt;p class="head"&gt;&lt;b&gt;Notification of Change&lt;/b&gt;&lt;/p&gt;
-&lt;hr /&gt;
-&lt;table class="demoDiv" style="width: 85%; border-spacing: 10px;"&gt;
-    &lt;tr&gt;
-        #set( $counter = 0 )
-        #set( $orderedFields = [ 
-                    "surname",  
-                    "givenName",  
-                    "otherNames",  
-                    "maidenName",  
-                    "previousName",  
-                    "isErrorNameChange",  
-                    "changeReasonNameChange",  
-                    "removeOtherNames",  
-                    "removeMaidenName",  
-                    "removePreviousName",  
-                    "isErrorNameRemove",  
-                    "changeReasonNameRemove",  
-                    "dateOfBirth",  
-                    "isErrorChangeOfDateOfBirth",  
-                    "residenceStatus",  
-                    "applicantForeignResidenceCountry",  
-                    "applicantForeignResidenceAddress",  
-                    "appResCountryUGA",  
-                    "applicantPlaceOfResidenceDistrict",  
-                    "applicantPlaceOfResidenceCounty",  
-                    "applicantPlaceOfResidenceSubCounty",  
-                    "applicantPlaceOfResidenceParish",  
-                    "applicantPlaceOfResidenceVillage",  
-                    "applicantPlaceOfResidenceStreet",  
-                    "applicantPlaceOfResidenceHouseNo",  
-                    "applicantPlaceOfResidenceYearsLived",  
-                    "applicantPlaceOfResidenceDistrictOfPrevRes",  
-                    "applicantPlaceOfResidencePostalAddress",  
-                    "isErrorChangeInPlaceOfResidence",  
-                    "applicantBirthPlace",  
-                    "applicantForeignBirthCountry",  
-                    "applicantForeignBirthAddress",  
-                    "appBirCountryUGA",  
-                    "applicantPlaceOfBirthDistrict",  
-                    "applicantPlaceOfBirthCounty",  
-                    "applicantPlaceOfBirthSubCounty",  
-                    "applicantPlaceOfBirthParish",  
-                    "applicantPlaceOfBirthVillage",  
-                    "applicantPlaceOfBirthCity",  
-                    "applicantPlaceOfBirthHealthFacility",  
-                    "isErrorChangeInPlaceOfBirth",  
-                    "applicantOriginPlace",  
-                    "applicantForeignOriginCountry",  
-                    "applicantForeignOriginAddress",  
-                    "appOriCountryUGA",  
-                    "applicantPlaceOfOriginDistrict",  
-                    "applicantPlaceOfOriginCounty",  
-                    "applicantPlaceOfOriginSubCounty",  
-                    "applicantPlaceOfOriginParish",  
-                    "applicantPlaceOfOriginVillage",  
-                    "applicantPlaceOfOriginIndigenousCommunityTribe",  
-                    "applicantPlaceOfOriginClan",  
-                    "isErrorChangeInPlaceOfOrigin",  
-                    "citizenshipType",  
-                    "isErrorChangeInCitizenshipType",  
-                    "numberOfOtherSpouses",  
-                    "spouseSurname",  
-                    "spouseGivenName",  
-                    "spouseOtherNames",  
-                    "spouseMaidenName",  
-                    "spousePreviousName",  
-                    "spouseNIN",  
-                    "spouseCitizenshipType",  
-                    "spousePlaceOfMarriage",  
-                    "spouseDateOfMarriage",  
-                    "spouseTypeOfMarriage",  
-                    "spouseMarriageCertificateNumber",  
-                    "spouseTwoSurname",  
-                    "spouseTwoGivenName",  
-                    "spouseTwoOtherNames",  
-                    "spouseTwoMaidenName",  
-                    "spouseTwoPreviousName",  
-                    "spouseTwoNIN",  
-                    "spouseTwoCitizenshipType",  
-                    "spouseTwoPlaceOfMarriage",  
-                    "spouseTwoDateOfMarriage",  
-                    "spouseTwoTypeOfMarriage",  
-                    "spouseTwoMarriageCertificateNumber",  
-                    "spouseThreeSurname",  
-                    "spouseThreeGivenName",  
-                    "spouseThreeOtherNames",  
-                    "spouseThreeMaidenName",  
-                    "spouseThreePreviousName",  
-                    "spouseThreeNIN",  
-                    "spouseThreeCitizenshipType",  
-                    "spouseThreePlaceOfMarriage",  
-                    "spouseThreeDateOfMarriage",  
-                    "spouseThreeTypeOfMarriage",  
-                    "spouseThreeMarriageCertificateNumber",  
-                    "spouseFourSurname",  
-                    "spouseFourGivenName",  
-                    "spouseFourOtherNames",  
-                    "spouseFourMaidenName",  
-                    "spouseFourPreviousName",  
-                    "spouseFourNIN",  
-                    "spouseFourCitizenshipType",  
-                    "spouseFourPlaceOfMarriage",  
-                    "spouseFourDateOfMarriage",  
-                    "spouseFourTypeOfMarriage",  
-                    "spouseFourMarriageCertificateNumber",  
-                    "isErrorAddSpouse",  
-                    "removeSpouseGivenName",  
-                    "removeSpouseDateOfMarriage",  
-                    "isErrorRemoveSpouse",  
-                    "fatherLivingStatus",  
-                    "fatherSurname",  
-                    "fatherGivenName",  
-                    "fatherOtherNames",  
-                    "fatherPreviousName",  
-                    "fatherNIN",  
-                    "fatherIDDocumentNo",  
-                    "fatherOccupation",  
-                    "fatherCitizenshipType",  
-                    "fatherCitizenCertificateNumber",  
-                    "fatherResidence",  
-                    "fatherForeignResidenceCountry",  
-                    "fatherForeignResidenceAddress",  
-                    "fatherPostalAddress",  
-                    "fatResCountryUGA",  
-                    "fatherPlaceOfResidenceDistrict",  
-                    "fatherPlaceOfResidenceCounty",  
-                    "fatherPlaceOfResidenceSubCounty",  
-                    "fatherPlaceOfResidenceParish",  
-                    "fatherPlaceOfResidenceVillage",  
-                    "fatherPlaceOfResidenceStreet",  
-                    "fatherPlaceOfResidenceHouseNo",  
-                    "fatherOrigin",  
-                    "sameAsFatherPlaceOfResidenceCheckBox",  
-                    "sameAsFatherPlaceOfResidenceCheckBoxOutsideUganda",  
-                    "fatherForeignOriginCountry",  
-                    "fatherForeignOriginAddress",  
-                    "fatOriCountryUGA",  
-                    "fatherPlaceOfOriginDistrict",  
-                    "fatherPlaceOfOriginCounty",  
-                    "fatherPlaceOfOriginSubCounty",  
-                    "fatherPlaceOfOriginParish",  
-                    "fatherPlaceOfOriginVillage",  
-                    "fatherIndigenousCommunityTribe",  
-                    "fatherIndigenousCommunityClan",  
-                    "isErrorChangeDetailsOfFather",  
-                    "motherLivingStatus",  
-                    "motherSurname",  
-                    "motherGivenName",  
-                    "motherOtherNames",  
-                    "motherMaidenName",  
-                    "motherPreviousName",  
-                    "motherNIN",  
-                    "motherIDDocumentNo",  
-                    "motherCitizenshipType",  
-                    "motherCitizenCertificateNumber",  
-                    "motherOccupation",  
-                    "motherResidence",  
-                    "motherForeignResidenceCountry",  
-                    "motherForeignResidenceAddress",  
-                    "motherPostalAddress",  
-                    "motResCountryUGA",  
-                    "motherPlaceOfResidenceDistrict",  
-                    "motherPlaceOfResidenceCounty",  
-                    "motherPlaceOfResidenceSubCounty",  
-                    "motherPlaceOfResidenceParish",  
-                    "motherPlaceOfResidenceVillage",  
-                    "motherPlaceOfResidenceStreet",  
-                    "motherPlaceOfResidenceHouseNo",  
-                    "motherOrigin",  
-                    "sameAsMotherPlaceOfResidenceCheckBox",  
-                    "sameAsMotherPlaceOfResidenceCheckBoxOutsideUganda",  
-                    "motherForeignOriginCountry",  
-                    "motherForeignOriginAddress",  
-                    "motOriCountryUGA",  
-                    "motherPlaceOfOriginDistrict",  
-                    "motherPlaceOfOriginCounty",  
-                    "motherPlaceOfOriginSubCounty",  
-                    "motherPlaceOfOriginParish",  
-                    "motherPlaceOfOriginVillage",  
-                    "motherIndigenousCommunityTribe",  
-                    "motherIndigenousCommunityClan",  
-                    "isErrorChangeDetailsOfMother",  
-                    "errorRegardingNIN",  
-                    "isErrorCorrectionOfErrorRegardingNin"
-         ] ) &lt;!-- Define the order of fields --&gt;
-    &lt;tr&gt; &lt;!-- Start the first row --&gt;
-        #foreach( $field in $orderedFields )
-         #if( $demographics.containsKey($field) &amp;&amp; $demographics.get($field).get("value") )
-        &lt;!-- Check if the field exists , has a value and not N/A --&gt;
-        &lt;td style="vertical-align: top; width: 28%;"&gt;
-            &lt;p class="headings"&gt;&lt;b&gt;$demographics.get($field).get("label")&lt;/b&gt;&lt;/p&gt;&lt;br /&gt;
-            &lt;p&gt;$demographics.get($field).get("value")&lt;/p&gt;
-        &lt;/td&gt;
-        #set( $counter = $counter + 1 )
-        #if( $counter % 3 == 0 )
-    &lt;/tr&gt;
-    &lt;tr&gt; &lt;!-- Close current row and start a new one after 3 fields --&gt;
-        #end
-        #end
-        #end
-    &lt;/tr&gt; &lt;!-- Close the last row --&gt;
-    &lt;/tr&gt;
-&lt;/table&gt;
-&lt;div style="width: 100%; height: 50%; clear:both"&gt;&lt;/div&gt;
-&lt;br&gt; &lt;br /&gt;
-&lt;hr /&gt;
-            &lt;p class="head"&gt;&lt;b&gt;Signature&lt;/b&gt;&lt;/p&gt;
-            &lt;hr /&gt;
-            &lt;table class="dataTable"&gt;
-                &lt;!-- Check if "applicantProofOfSignature" exists --&gt;
-                #if ($demographics.containsKey("applicantProofOfSignature") &amp;&amp; $demographics.get("applicantProofOfSignature").get("value") )
-                &lt;tr&gt;
-                    &lt;td style="vertical-align: top; width: 50%;"&gt;
-                        &lt;p class="headings"&gt;&lt;b&gt;$demographics.get("applicantProofOfSignature").get("label")&lt;/b&gt;&lt;/p&gt;&lt;br /&gt;
-                        &lt;img src="$demographics.get("applicantProofOfSignature").get("signature")" width=120 height=80 /&gt;
-                    &lt;/td&gt;
-                &lt;/tr&gt;
-                &lt;!-- Check if "applicantUnabletoSign" exists --&gt;
-                #elseif ($demographics.containsKey("applicantUnabletoSign") &amp;&amp; $demographics.get("applicantUnabletoSign").get("value") == 'Y')
-                &lt;tr&gt;
-                    &lt;td style="vertical-align: top; width: 50%;"&gt;
-                        &lt;p class="headings"&gt;&lt;b&gt;$demographics.get("applicantUnabletoSign").get("label")&lt;/b&gt;&lt;/p&gt;&lt;br /&gt;
-                        &lt;p&gt;Unable to Sign&lt;/p&gt;
-                    &lt;/td&gt;
-                &lt;/tr&gt;
-                #elseif ($demographics.containsKey("introducerProofOfSignature") &amp;&amp; $demographics.get("introducerProofOfSignature").get("value"))
-                &lt;tr&gt;
-                    &lt;td style="vertical-align: top; width: 50%;"&gt;
-                        &lt;p class="headings"&gt;&lt;b&gt;$demographics.get("introducerProofOfSignature").get("label")&lt;/b&gt;&lt;/p&gt;&lt;br /&gt;
-                        &lt;img src="$demographics.get("introducerProofOfSignature").get("introducerSignature")" width=120 height=80 /&gt;
-                    &lt;/td&gt;
-                &lt;/tr&gt;
-                &lt;!-- Check if "applicantUnabletoSign" exists --&gt;
-                #elseif ($demographics.containsKey("introducerUnabletoSign") &amp;&amp; $demographics.get("introducerUnabletoSign").get("value") == 'Y')
-                &lt;tr&gt;
-                    &lt;td style="vertical-align: top; width: 50%;"&gt;
-                        &lt;p class="headings"&gt;&lt;b&gt;$demographics.get("introducerUnabletoSign").get("label")&lt;/b&gt;&lt;/p&gt;&lt;br /&gt;
-                        &lt;p&gt;Unable to Sign&lt;/p&gt;
-                    &lt;/td&gt;
-                &lt;/tr&gt;
-                #end
-            &lt;/table&gt;
-            &lt;hr /&gt;
-            &lt;p class=head&gt;&lt;b&gt;${DocumentsLabel}&lt;/b&gt;&lt;/p&gt;
-            &lt;hr /&gt;
-            &lt;table class=dataTable&gt;
-                #foreach( $key in $documents.keySet() )
-                &lt;tr&gt;
-                    &lt;td&gt;
-                        &lt;p class=headings&gt;$documents.get($key).get("label")&lt;/p&gt;
-                        &lt;br /&gt;
-                        &lt;p&gt; $documents.get($key).get("value")&lt;/p&gt;
-                    &lt;/td&gt;
-                &lt;/tr&gt;
-                #end
-            &lt;/table&gt;
-            &lt;br /&gt;
-            &lt;hr /&gt;
-            &lt;p class=head&gt;&lt;b&gt;${BiometricsLabel}&lt;/b&gt;&lt;/p&gt;
-            &lt;hr /&gt;
-            #foreach( $key in $biometrics.keySet() )
-            &lt;table&gt;
-                &lt;tr&gt;
-                    &lt;td&gt;
-                        $biometrics.get($key).get("label")&lt;br /&gt;
-                        &lt;p class=headings&gt;${Fingers} ( $biometrics.get($key).get("FingerCount") ),${Iris} (
-                            $biometrics.get($key).get("IrisCount") ),${Face} ( $biometrics.get($key).get("FaceCount")
-                            )&lt;br /&gt;&lt;/p&gt;
-                        &lt;br /&gt;
-                    &lt;/td&gt;
-                &lt;/tr&gt;
-                &lt;table class=biometricsTable&gt;
-                    &lt;tr&gt;
-                        #if( $biometrics.get($key).get("CapturedLeftEye") )
-                        &lt;td&gt;
-                            &lt;p class=headings&gt;${LeftEyeLabel}&lt;/p&gt;
-                        &lt;/td&gt;
-                        #end #if( $biometrics.get($key).get("CapturedRightEye") )
-                        &lt;td&gt;
-                            &lt;p class=headings&gt;${RightEyeLabel}&lt;/p&gt;
-                        &lt;/td&gt;
-                        #end
-                    &lt;/tr&gt;
-                    &lt;tr&gt;
-                        #if( $biometrics.get($key).get("CapturedLeftEye") )
-                        &lt;td&gt; #if( $biometrics.get($key).get("CapturedLeftEye") ) &lt;img
-                                src=$biometrics.get($key).get("CapturedLeftEye") border=0 width=85 height=80 /&gt; #end
-                        &lt;/td&gt;
-                        #end #if( $biometrics.get($key).get("CapturedRightEye") )
-                        &lt;td&gt; #if( $biometrics.get($key).get("CapturedRightEye") ) &lt;img
-                                src=$biometrics.get($key).get("CapturedRightEye") border=0 width=85 height=80 /&gt; #end
-                        &lt;/td&gt;
-                        #end
-                    &lt;/tr&gt;
-                &lt;/table&gt;
-                &lt;table class=biometricsTable&gt;
-                    &lt;tr&gt;
-                        #if( $biometrics.get($key).get("CapturedLeftSlap") )
-                        &lt;td&gt;
-                            &lt;p class=headings&gt;${LeftPalmLabel}&lt;/p&gt;
-                        &lt;/td&gt;
-                        #end #if( $biometrics.get($key).get("CapturedRightSlap") )
-                        &lt;td&gt;
-                            &lt;p class=headings&gt;${RightPalmLabel}&lt;/p&gt;
-                        &lt;/td&gt;
-                        #end #if( $biometrics.get($key).get("CapturedThumbs") )
-                        &lt;td&gt;
-                            &lt;p class=headings&gt;${ThumbsLabel}&lt;/p&gt;
-                        &lt;/td&gt;
-                        #end
-                    &lt;/tr&gt;
-                    &lt;tr&gt;
-                        #if( $biometrics.get($key).get("CapturedLeftSlap") )
-                        &lt;td style="text-align:-webkit-center"&gt; &lt;img src=$biometrics.get($key).get("CapturedLeftSlap")
-                                border=0 width=85 height=80 /&gt; &lt;/td&gt;
-                        #end #if( $biometrics.get($key).get("CapturedRightSlap") )
-                        &lt;td style="text-align:-webkit-center"&gt; &lt;img src=$biometrics.get($key).get("CapturedRightSlap")
-                                border=0 width=85 height=80 /&gt; &lt;/td&gt;
-                        #end #if( $biometrics.get($key).get("CapturedThumbs") )
-                        &lt;td style="text-align:-webkit-center"&gt; &lt;img src=$biometrics.get($key).get("CapturedThumbs")
-                                border=0 width=85 height=80 /&gt; &lt;/td&gt;
-                        #end
-                    &lt;/tr&gt;
-                &lt;/table&gt;
-                &lt;br /&gt;
-                &lt;table class=biometricsTable&gt;
-                    &lt;tr&gt;
-                        #if( $biometrics.get($key).get("FaceImageSource") )
-                        &lt;td&gt;
-                            &lt;p class=headings&gt;${FaceLabel}&lt;/p&gt;
-                        &lt;/td&gt;
-                        #end #if( $biometrics.get($key).get("subType") == "applicant" &amp;&amp; $ExceptionImageSource )
-                        &lt;td&gt;
-                            &lt;p class=headings&gt;${ExceptionPhotoLabel}&lt;/p&gt;
-                        &lt;/td&gt;
-                        #end
-                    &lt;/tr&gt;
-                    &lt;tr&gt;
-                        #if( $biometrics.get($key).get("FaceImageSource") )
-                        &lt;td&gt; &lt;img src=$biometrics.get($key).get("FaceImageSource") border=0 width=85 height=80 /&gt; &lt;/td&gt;
-                        #end #if( $biometrics.get($key).get("subType") == "applicant" &amp;&amp; $ExceptionImageSource )
-                        &lt;td&gt; &lt;img src=${ExceptionImageSource} border=0 width=85 height=80 /&gt; &lt;/td&gt;
-                        #end
-                    &lt;/tr&gt;
-                &lt;/table&gt;
-            &lt;/table&gt;
-            #end &lt;br /&gt;
-            &lt;hr /&gt; &lt;br /&gt;
-        &lt;/div&gt;
-        &lt;div&gt;
-            &lt;p class="head"&gt;${ImportantGuidelines}&lt;/p&gt;
-            &lt;ol&gt;
-                &lt;li&gt;&lt;span&gt;Your application has been successfully submitted for review.&lt;/span&gt;&lt;/li&gt;
-                &lt;li&gt;&lt;span&gt;All demographics, documents, and biometrics have been received and are under
-                        verification.&lt;/span&gt;&lt;/li&gt;
-                &lt;li&gt;&lt;span&gt;You will receive updates on the progress via SMS/Email.&lt;/span&gt;&lt;/li&gt;
-                &lt;li&gt;&lt;span&gt;Contact support or visit the nearest enrollment center if assistance is required.&lt;/span&gt;&lt;/li&gt;
-            &lt;/ol&gt;
-        &lt;/div&gt;
-&lt;/body&gt;
-&lt;/html&gt;</t>
   </si>
   <si>
     <t>reg-cop-preview-template-part</t>
@@ -7506,6 +6852,660 @@
   <si>
     <t>Dear $name your Pre-Registration for NIN is Completed Successfully on $Date at $Time. Your ID is $!PRID.</t>
   </si>
+  <si>
+    <t>&lt;!DOCTYPE html&gt;
+&lt;html $rtl&gt;
+&lt;head&gt;
+    &lt;style&gt;
+        body {
+            font-family: "Roboto";
+        }
+        table,
+        .head {
+            font-size: 13px;
+        }
+        .demoDiv {
+            width: 85%;
+            float: left;
+            padding: 1.5px;
+        }
+        .photoDiv {
+            width: 15%;
+            float: right;
+        }
+        .form {
+            display: inline-block;
+        }
+        .section {
+            align: center;
+            padding: 30px;
+            width: 800px;
+            margin: auto;
+        }
+        .headings {
+            color: #808080;
+            font-size: 12px;
+        }
+        p {
+            display: inline;
+        }
+        .dataTable {
+            word-wrap: break-word;
+            table-layout: fixed;
+            width: 70%;
+        }
+        .headerTable {
+            width: 90%;
+        }
+        .NINHeaderTable {
+            width: 100%;
+        }
+        h5 {
+            display: inline;
+            position: absolute;
+        }
+        .iris {
+            top: -15px;
+            left: 152px;
+        }
+        .irisWithoutException {
+            top: -15px;
+            left: 114px;
+        }
+        .tableWithoutException {
+            width: 50%;
+            text-align: center;
+            table-layout: fixed;
+            margin: 0 auto;
+        }
+        .biometricsTable {
+            width: 100%;
+            text-align: center;
+            table-layout: fixed;
+        }
+        .biometrics {
+            position: relative;
+        }
+        .leftLittle {
+            top: 15px;
+            left: 11px;
+            display: inline;
+            position: absolute;
+        }
+        .leftRing {
+            top: 3px;
+            left: 23px;
+        }
+        .leftMiddle {
+            top: -7px;
+            left: 37px;
+        }
+        .leftIndex {
+            top: 3px;
+            left: 54px;
+        }
+        .rightIndex {
+            top: 3px;
+            left: 26px;
+        }
+        .rightMiddle {
+            top: -7px;
+            left: 39px;
+        }
+        .rightRing {
+            top: 3px;
+            left: 55px;
+        }
+        .rightLittle {
+            top: 15px;
+            left: 68px;
+        }
+        .leftThumb {
+            top: -4px;
+            left: 24px;
+        }
+        .rightThumb {
+            top: -4px;
+            left: 54px;
+        }
+        .parentStyle {
+            top: -15px;
+            left: 152px;
+        }
+        .parentIris1 {
+            top: -15px;
+            left: 212px;
+        }
+        .parentIris2 {
+            top: -15px;
+            left: 214px;
+        }
+        li span {
+            color: black;
+            font-size: 12px;
+        }
+        li {
+            color: #808080;
+        }
+        button {
+            float: right;
+            font-size: 12px;
+            border: none;
+            background-color: transparent;
+            outline: none;
+        }
+        button:active {
+            background-color: black;
+            color: white;
+        }
+        .bottom {
+            vertical-align: bottom;
+        }
+        .consent-block {
+            font-size: 13px;
+            border-radius: 8px;
+            margin-top: 10px;
+            margin-bottom: 10px;
+            border: 2px solid #E88E3F;
+            padding-top: -50px;
+            padding: 10px;
+        }
+        .consent-text {
+            margin-left: 7px;
+            margin-bottom: 4px;
+        }
+        input[type="radio"] {
+            display: none;
+        }
+        input[type="radio"]+label:before {
+            content: "";
+            display: inline-block;
+            width: 15px;
+            height: 15px;
+            padding: 3px;
+            margin-right: 5px;
+            background-clip: content-box;
+            /* border: 1px solid grey; */
+            background-color: #fff;
+            border-radius: 50%;
+        }
+        input[type="radio"]:checked+label:before {
+            background-color: #FF4081;
+            border-color: #FF4081;
+        }
+        *,
+        *:before,
+        *:after {
+            box-sizing: border-box;
+        }
+        .consent-block label {
+            display: inline-flex;
+            align-items: center;
+        }
+        /* .demoDiv&gt;table {
+            width: 100%
+        } */
+        /* .demoDiv&gt;table&gt;tbody&gt;tr&gt;th {
+            color: #808080;
+            font-size: 10px;
+            width: 25%;
+            text-align: left;
+            padding: 1.5px;
+        }
+        .demoDiv&gt;table&gt;tbody&gt;tr&gt;td {
+            font-size: 12px;
+            width: 25%;
+            text-align: left;
+            padding: 2px;
+        } */
+        ol {
+            font-size: 12px;
+        }
+    &lt;/style&gt;
+    &lt;script&gt;function changeColour(element) { var div = document.getElementById("radioId"); if (element.value == "yes") { div.style = "border: 2px solid #68A933"; } if (element.value == "no") { div.style = "border: 2px solid #FF0000"; } } document.onreadystatechange = function () { if (document.readyState === "complete") { var body = document.getElementsByTagName("body")[0]; body.addEventListener("dragstart", function (event) { event.preventDefault(); }); body.addEventListener("selectstart", function (event) { event.preventDefault(); }); } }&lt;/script&gt;
+&lt;/head&gt;
+&lt;body&gt;
+    &lt;div class=section&gt;
+        &lt;div class=form&gt;
+            &lt;table class=headerTable&gt;
+                &lt;tr&gt;
+                    &lt;td class=bottom&gt;
+                        &lt;p class=headings&gt;${ApplicationIDLabel}&lt;/p&gt;
+                        &lt;br /&gt;${ApplicationID}
+                    &lt;/td&gt;
+                    &lt;td class=bottom&gt;
+                        &lt;p class=headings&gt;${DateLabel}&lt;/p&gt;
+                        &lt;br /&gt;${Date}
+                    &lt;/td&gt;
+                &lt;/tr&gt;
+            &lt;/table&gt;
+            &lt;br /&gt; #if ( $name )
+            &lt;table class=headerTable&gt;
+                &lt;tr&gt;
+                    &lt;td&gt;
+                        &lt;p class=headings&gt;${NameLabel}&lt;/p&gt;
+                        &lt;br /&gt;${NameValue}
+                    &lt;/td&gt;
+                &lt;/tr&gt;
+            &lt;/table&gt;
+            #end &lt;br /&gt;
+            &lt;hr /&gt;
+            &lt;p class="head"&gt;&lt;b&gt;${DemographicInfo}&lt;/b&gt;&lt;/p&gt;
+            &lt;hr /&gt;
+            &lt;table class="demoDiv" style="width: 85%; border-spacing: 10px;"&gt;
+                &lt;tr&gt;
+                    #set( $counter = 0 )
+                    #set( $orderedFields = [ "surnameCop",
+                    "givenNameCop",
+                    "otherNamesCop",
+                    "genderCop",
+                    "dateOfBirthCop",
+                    "NIN",
+                    "email",
+                    "CountryCode",
+                    "phone",
+                    "homePhoneNumber",
+                    "nameOfNextOfKin",
+                    "telephoneNumberOfNextOfKin",
+                    "emailOfNextOfKin"
+                     ] ) &lt;!-- Define the order of fields --&gt;
+                &lt;tr&gt; &lt;!-- Start the first row --&gt;
+                    #foreach( $field in $orderedFields )
+                       #if( $demographics.containsKey($field) &amp;&amp; $demographics.get($field).get("value") &amp;&amp; $demographics.get($field).get("value") != "N" )
+                    &lt;!-- Check if the field exists and has a value --&gt;
+                    &lt;td style="vertical-align: top; width: 28%;"&gt;
+                        &lt;p class="headings"&gt;&lt;b&gt;$demographics.get($field).get("label")&lt;/b&gt;&lt;/p&gt;&lt;br /&gt;
+                        &lt;p&gt;$demographics.get($field).get("value")&lt;/p&gt;
+                    &lt;/td&gt;
+                    #set( $counter = $counter + 1 )
+                    #if( $counter % 3 == 0 )
+                &lt;/tr&gt;
+                &lt;tr&gt; &lt;!-- Close current row and start a new one after 3 fields --&gt;
+                    #end
+                    #end
+                    #end
+                &lt;/tr&gt; &lt;!-- Close the last row --&gt;
+                &lt;/tr&gt;
+            &lt;/table&gt;
+            #if ( $ApplicantImageSource )
+            &lt;!-- &lt;div class="photoDiv" style="vertical-align: top; float: right;"&gt; --&gt;
+            &lt;table style="vertical-align: top; float: right;  width: 15%;"&gt;
+                &lt;tr&gt;
+                    &lt;td&gt;
+                        &lt;p&gt;${Photo}&lt;/p&gt;
+                    &lt;/td&gt;
+                &lt;/tr&gt;
+                &lt;tr&gt;
+                    &lt;td&gt;&lt;img src=${ApplicantImageSource} width=100 height=100 /&gt;&lt;/td&gt;
+                &lt;/tr&gt;
+            &lt;/table&gt;
+            #end
+            &lt;div style="width: 100%; height: 50%; clear:both"&gt;&lt;/div&gt;
+            &lt;br&gt; &lt;br /&gt;
+            &lt;hr /&gt;
+            &lt;p class="head"&gt;&lt;b&gt;Notification of Change&lt;/b&gt;&lt;/p&gt;
+&lt;hr /&gt;
+&lt;table class="demoDiv" style="width: 85%; border-spacing: 10px;"&gt;
+    &lt;tr&gt;
+        #set( $counter = 0 )
+        #set( $orderedFields = [ 
+                    "surname",  
+                    "givenName",  
+                    "otherNames",  
+                    "maidenName",  
+                    "previousName",  
+                    "isErrorNameChange",  
+                    "changeReasonNameChange",  
+                    "removeOtherNames",  
+                    "removeMaidenName",  
+                    "removePreviousName",  
+                    "isErrorNameRemove",  
+                    "changeReasonNameRemove",  
+                    "dateOfBirth",  
+                    "isErrorChangeOfDateOfBirth",  
+                    "residenceStatus",  
+                    "applicantForeignResidenceCountry",  
+                    "applicantForeignResidenceAddress",  
+                    "appResCountryUGA",  
+                    "applicantPlaceOfResidenceDistrict",  
+                    "applicantPlaceOfResidenceCounty",  
+                    "applicantPlaceOfResidenceSubCounty",  
+                    "applicantPlaceOfResidenceParish",  
+                    "applicantPlaceOfResidenceVillage",  
+                    "applicantPlaceOfResidenceStreet",  
+                    "applicantPlaceOfResidenceHouseNo",  
+                    "applicantPlaceOfResidenceYearsLived",  
+                    "applicantPlaceOfResidenceDistrictOfPrevRes",  
+                    "applicantPlaceOfResidencePostalAddress",  
+                    "isErrorChangeInPlaceOfResidence",  
+                    "applicantBirthPlace",  
+                    "applicantForeignBirthCountry",  
+                    "applicantForeignBirthAddress",  
+                    "appBirCountryUGA",  
+                    "applicantPlaceOfBirthDistrict",  
+                    "applicantPlaceOfBirthCounty",  
+                    "applicantPlaceOfBirthSubCounty",  
+                    "applicantPlaceOfBirthParish",  
+                    "applicantPlaceOfBirthVillage",  
+                    "applicantPlaceOfBirthCity",  
+                    "applicantPlaceOfBirthHealthFacility",  
+                    "isErrorChangeInPlaceOfBirth",  
+                    "applicantOriginPlace",  
+                    "applicantForeignOriginCountry",  
+                    "applicantForeignOriginAddress",  
+                    "appOriCountryUGA",  
+                    "applicantPlaceOfOriginDistrict",  
+                    "applicantPlaceOfOriginCounty",  
+                    "applicantPlaceOfOriginSubCounty",  
+                    "applicantPlaceOfOriginParish",  
+                    "applicantPlaceOfOriginVillage",  
+                    "applicantPlaceOfOriginIndigenousCommunityTribe",  
+                    "applicantPlaceOfOriginClan",  
+                    "isErrorChangeInPlaceOfOrigin",  
+                    "citizenshipType",  
+                    "isErrorChangeInCitizenshipType",  
+                    "numberOfOtherSpouses",  
+                    "spouseSurname",  
+                    "spouseGivenName",  
+                    "spouseOtherNames",  
+                    "spouseMaidenName",  
+                    "spousePreviousName",  
+                    "spouseNIN",  
+                    "spouseCitizenshipType",  
+                    "spousePlaceOfMarriage",  
+                    "spouseDateOfMarriage",  
+                    "spouseTypeOfMarriage",  
+                    "spouseMarriageCertificateNumber",  
+                    "spouseTwoSurname",  
+                    "spouseTwoGivenName",  
+                    "spouseTwoOtherNames",  
+                    "spouseTwoMaidenName",  
+                    "spouseTwoPreviousName",  
+                    "spouseTwoNIN",  
+                    "spouseTwoCitizenshipType",  
+                    "spouseTwoPlaceOfMarriage",  
+                    "spouseTwoDateOfMarriage",  
+                    "spouseTwoTypeOfMarriage",  
+                    "spouseTwoMarriageCertificateNumber",  
+                    "spouseThreeSurname",  
+                    "spouseThreeGivenName",  
+                    "spouseThreeOtherNames",  
+                    "spouseThreeMaidenName",  
+                    "spouseThreePreviousName",  
+                    "spouseThreeNIN",  
+                    "spouseThreeCitizenshipType",  
+                    "spouseThreePlaceOfMarriage",  
+                    "spouseThreeDateOfMarriage",  
+                    "spouseThreeTypeOfMarriage",  
+                    "spouseThreeMarriageCertificateNumber",  
+                    "spouseFourSurname",  
+                    "spouseFourGivenName",  
+                    "spouseFourOtherNames",  
+                    "spouseFourMaidenName",  
+                    "spouseFourPreviousName",  
+                    "spouseFourNIN",  
+                    "spouseFourCitizenshipType",  
+                    "spouseFourPlaceOfMarriage",  
+                    "spouseFourDateOfMarriage",  
+                    "spouseFourTypeOfMarriage",  
+                    "spouseFourMarriageCertificateNumber",  
+                    "isErrorAddSpouse",  
+                    "removeSpouseGivenName",  
+                    "removeSpouseDateOfMarriage",  
+                    "isErrorRemoveSpouse",  
+                    "fatherLivingStatus",  
+                    "fatherSurname",  
+                    "fatherGivenName",  
+                    "fatherOtherNames",  
+                    "fatherPreviousName",  
+                    "fatherNIN",  
+                    "fatherIDDocumentNo",  
+                    "fatherOccupation",  
+                    "fatherCitizenshipType",  
+                    "fatherCitizenCertificateNumber",  
+                    "fatherResidence",  
+                    "fatherForeignResidenceCountry",  
+                    "fatherForeignResidenceAddress",  
+                    "fatherPostalAddress",  
+                    "fatResCountryUGA",  
+                    "fatherPlaceOfResidenceDistrict",  
+                    "fatherPlaceOfResidenceCounty",  
+                    "fatherPlaceOfResidenceSubCounty",  
+                    "fatherPlaceOfResidenceParish",  
+                    "fatherPlaceOfResidenceVillage",  
+                    "fatherPlaceOfResidenceStreet",  
+                    "fatherPlaceOfResidenceHouseNo",  
+                    "fatherOrigin",  
+                    "sameAsFatherPlaceOfResidenceCheckBox",  
+                    "sameAsFatherPlaceOfResidenceCheckBoxOutsideUganda",  
+                    "fatherForeignOriginCountry",  
+                    "fatherForeignOriginAddress",  
+                    "fatOriCountryUGA",  
+                    "fatherPlaceOfOriginDistrict",  
+                    "fatherPlaceOfOriginCounty",  
+                    "fatherPlaceOfOriginSubCounty",  
+                    "fatherPlaceOfOriginParish",  
+                    "fatherPlaceOfOriginVillage",  
+                    "fatherIndigenousCommunityTribe",  
+                    "fatherIndigenousCommunityClan",  
+                    "isErrorChangeDetailsOfFather",  
+                    "motherLivingStatus",  
+                    "motherSurname",  
+                    "motherGivenName",  
+                    "motherOtherNames",  
+                    "motherMaidenName",  
+                    "motherPreviousName",  
+                    "motherNIN",  
+                    "motherIDDocumentNo",  
+                    "motherCitizenshipType",  
+                    "motherCitizenCertificateNumber",  
+                    "motherOccupation",  
+                    "motherResidence",  
+                    "motherForeignResidenceCountry",  
+                    "motherForeignResidenceAddress",  
+                    "motherPostalAddress",  
+                    "motResCountryUGA",  
+                    "motherPlaceOfResidenceDistrict",  
+                    "motherPlaceOfResidenceCounty",  
+                    "motherPlaceOfResidenceSubCounty",  
+                    "motherPlaceOfResidenceParish",  
+                    "motherPlaceOfResidenceVillage",  
+                    "motherPlaceOfResidenceStreet",  
+                    "motherPlaceOfResidenceHouseNo",  
+                    "motherOrigin",  
+                    "sameAsMotherPlaceOfResidenceCheckBox",  
+                    "sameAsMotherPlaceOfResidenceCheckBoxOutsideUganda",  
+                    "motherForeignOriginCountry",  
+                    "motherForeignOriginAddress",  
+                    "motOriCountryUGA",  
+                    "motherPlaceOfOriginDistrict",  
+                    "motherPlaceOfOriginCounty",  
+                    "motherPlaceOfOriginSubCounty",  
+                    "motherPlaceOfOriginParish",  
+                    "motherPlaceOfOriginVillage",  
+                    "motherIndigenousCommunityTribe",  
+                    "motherIndigenousCommunityClan",  
+                    "isErrorChangeDetailsOfMother",  
+                    "errorRegardingNIN",  
+                    "isErrorCorrectionOfErrorRegardingNin"
+         ] ) &lt;!-- Define the order of fields --&gt;
+    &lt;tr&gt; &lt;!-- Start the first row --&gt;
+        #foreach( $field in $orderedFields )
+         #if( $demographics.containsKey($field) &amp;&amp; $demographics.get($field).get("value") &amp;&amp; $demographics.get($field).get("value") != "N" )
+        &lt;!-- Check if the field exists , has a value and not N/A --&gt;
+        &lt;td style="vertical-align: top; width: 28%;"&gt;
+            &lt;p class="headings"&gt;&lt;b&gt;$demographics.get($field).get("label")&lt;/b&gt;&lt;/p&gt;&lt;br /&gt;
+            &lt;p&gt;$demographics.get($field).get("value")&lt;/p&gt;
+        &lt;/td&gt;
+        #set( $counter = $counter + 1 )
+        #if( $counter % 3 == 0 )
+    &lt;/tr&gt;
+    &lt;tr&gt; &lt;!-- Close current row and start a new one after 3 fields --&gt;
+        #end
+        #end
+        #end
+    &lt;/tr&gt; &lt;!-- Close the last row --&gt;
+    &lt;/tr&gt;
+&lt;/table&gt;
+&lt;div style="width: 100%; height: 50%; clear:both"&gt;&lt;/div&gt;
+&lt;br&gt; &lt;br /&gt;
+&lt;hr /&gt;
+            &lt;p class="head"&gt;&lt;b&gt;Signature&lt;/b&gt;&lt;/p&gt;
+            &lt;hr /&gt;
+            &lt;table class="dataTable"&gt;
+                &lt;!-- Check if "applicantProofOfSignature" exists --&gt;
+                #if ($demographics.containsKey("applicantProofOfSignature") &amp;&amp; $demographics.get("applicantProofOfSignature").get("value") )
+                &lt;tr&gt;
+                    &lt;td style="vertical-align: top; width: 50%;"&gt;
+                        &lt;p class="headings"&gt;&lt;b&gt;$demographics.get("applicantProofOfSignature").get("label")&lt;/b&gt;&lt;/p&gt;&lt;br /&gt;
+                        &lt;img src="$demographics.get("applicantProofOfSignature").get("signature")" width=120 height=80 /&gt;
+                    &lt;/td&gt;
+                &lt;/tr&gt;
+                &lt;!-- Check if "applicantUnabletoSign" exists --&gt;
+                #elseif ($demographics.containsKey("applicantUnabletoSign") &amp;&amp; $demographics.get("applicantUnabletoSign").get("value") == 'Y')
+                &lt;tr&gt;
+                    &lt;td style="vertical-align: top; width: 50%;"&gt;
+                        &lt;p class="headings"&gt;&lt;b&gt;$demographics.get("applicantUnabletoSign").get("label")&lt;/b&gt;&lt;/p&gt;&lt;br /&gt;
+                        &lt;p&gt;Unable to Sign&lt;/p&gt;
+                    &lt;/td&gt;
+                &lt;/tr&gt;
+                #elseif ($demographics.containsKey("introducerProofOfSignature") &amp;&amp; $demographics.get("introducerProofOfSignature").get("value"))
+                &lt;tr&gt;
+                    &lt;td style="vertical-align: top; width: 50%;"&gt;
+                        &lt;p class="headings"&gt;&lt;b&gt;$demographics.get("introducerProofOfSignature").get("label")&lt;/b&gt;&lt;/p&gt;&lt;br /&gt;
+                        &lt;img src="$demographics.get("introducerProofOfSignature").get("introducerSignature")" width=120 height=80 /&gt;
+                    &lt;/td&gt;
+                &lt;/tr&gt;
+                &lt;!-- Check if "applicantUnabletoSign" exists --&gt;
+                #elseif ($demographics.containsKey("introducerUnabletoSign") &amp;&amp; $demographics.get("introducerUnabletoSign").get("value") == 'Y')
+                &lt;tr&gt;
+                    &lt;td style="vertical-align: top; width: 50%;"&gt;
+                        &lt;p class="headings"&gt;&lt;b&gt;$demographics.get("introducerUnabletoSign").get("label")&lt;/b&gt;&lt;/p&gt;&lt;br /&gt;
+                        &lt;p&gt;Unable to Sign&lt;/p&gt;
+                    &lt;/td&gt;
+                &lt;/tr&gt;
+                #end
+            &lt;/table&gt;
+            &lt;hr /&gt;
+            &lt;p class=head&gt;&lt;b&gt;${DocumentsLabel}&lt;/b&gt;&lt;/p&gt;
+            &lt;hr /&gt;
+            &lt;table class=dataTable&gt;
+                #foreach( $key in $documents.keySet() )
+                &lt;tr&gt;
+                    &lt;td&gt;
+                        &lt;p class=headings&gt;$documents.get($key).get("label")&lt;/p&gt;
+                        &lt;br /&gt;
+                        &lt;p&gt; $documents.get($key).get("value")&lt;/p&gt;
+                    &lt;/td&gt;
+                &lt;/tr&gt;
+                #end
+            &lt;/table&gt;
+            &lt;br /&gt;
+            &lt;hr /&gt;
+            &lt;p class=head&gt;&lt;b&gt;${BiometricsLabel}&lt;/b&gt;&lt;/p&gt;
+            &lt;hr /&gt;
+            #foreach( $key in $biometrics.keySet() )
+            &lt;table&gt;
+                &lt;tr&gt;
+                    &lt;td&gt;
+                        $biometrics.get($key).get("label")&lt;br /&gt;
+                        &lt;p class=headings&gt;${Fingers} ( $biometrics.get($key).get("FingerCount") ),${Iris} (
+                            $biometrics.get($key).get("IrisCount") ),${Face} ( $biometrics.get($key).get("FaceCount")
+                            )&lt;br /&gt;&lt;/p&gt;
+                        &lt;br /&gt;
+                    &lt;/td&gt;
+                &lt;/tr&gt;
+                &lt;table class=biometricsTable&gt;
+                    &lt;tr&gt;
+                        #if( $biometrics.get($key).get("CapturedLeftEye") )
+                        &lt;td&gt;
+                            &lt;p class=headings&gt;${LeftEyeLabel}&lt;/p&gt;
+                        &lt;/td&gt;
+                        #end #if( $biometrics.get($key).get("CapturedRightEye") )
+                        &lt;td&gt;
+                            &lt;p class=headings&gt;${RightEyeLabel}&lt;/p&gt;
+                        &lt;/td&gt;
+                        #end
+                    &lt;/tr&gt;
+                    &lt;tr&gt;
+                        #if( $biometrics.get($key).get("CapturedLeftEye") )
+                        &lt;td&gt; #if( $biometrics.get($key).get("CapturedLeftEye") ) &lt;img
+                                src=$biometrics.get($key).get("CapturedLeftEye") border=0 width=85 height=80 /&gt; #end
+                        &lt;/td&gt;
+                        #end #if( $biometrics.get($key).get("CapturedRightEye") )
+                        &lt;td&gt; #if( $biometrics.get($key).get("CapturedRightEye") ) &lt;img
+                                src=$biometrics.get($key).get("CapturedRightEye") border=0 width=85 height=80 /&gt; #end
+                        &lt;/td&gt;
+                        #end
+                    &lt;/tr&gt;
+                &lt;/table&gt;
+                &lt;table class=biometricsTable&gt;
+                    &lt;tr&gt;
+                        #if( $biometrics.get($key).get("CapturedLeftSlap") )
+                        &lt;td&gt;
+                            &lt;p class=headings&gt;${LeftPalmLabel}&lt;/p&gt;
+                        &lt;/td&gt;
+                        #end #if( $biometrics.get($key).get("CapturedRightSlap") )
+                        &lt;td&gt;
+                            &lt;p class=headings&gt;${RightPalmLabel}&lt;/p&gt;
+                        &lt;/td&gt;
+                        #end #if( $biometrics.get($key).get("CapturedThumbs") )
+                        &lt;td&gt;
+                            &lt;p class=headings&gt;${ThumbsLabel}&lt;/p&gt;
+                        &lt;/td&gt;
+                        #end
+                    &lt;/tr&gt;
+                    &lt;tr&gt;
+                        #if( $biometrics.get($key).get("CapturedLeftSlap") )
+                        &lt;td style="text-align:-webkit-center"&gt; &lt;img src=$biometrics.get($key).get("CapturedLeftSlap")
+                                border=0 width=85 height=80 /&gt; &lt;/td&gt;
+                        #end #if( $biometrics.get($key).get("CapturedRightSlap") )
+                        &lt;td style="text-align:-webkit-center"&gt; &lt;img src=$biometrics.get($key).get("CapturedRightSlap")
+                                border=0 width=85 height=80 /&gt; &lt;/td&gt;
+                        #end #if( $biometrics.get($key).get("CapturedThumbs") )
+                        &lt;td style="text-align:-webkit-center"&gt; &lt;img src=$biometrics.get($key).get("CapturedThumbs")
+                                border=0 width=85 height=80 /&gt; &lt;/td&gt;
+                        #end
+                    &lt;/tr&gt;
+                &lt;/table&gt;
+                &lt;br /&gt;
+                &lt;table class=biometricsTable&gt;
+                    &lt;tr&gt;
+                        #if( $biometrics.get($key).get("FaceImageSource") )
+                        &lt;td&gt;
+                            &lt;p class=headings&gt;${FaceLabel}&lt;/p&gt;
+                        &lt;/td&gt;
+                        #end #if( $biometrics.get($key).get("subType") == "applicant" &amp;&amp; $ExceptionImageSource )
+                        &lt;td&gt;
+                            &lt;p class=headings&gt;${ExceptionPhotoLabel}&lt;/p&gt;
+                        &lt;/td&gt;
+                        #end
+                    &lt;/tr&gt;
+                    &lt;tr&gt;
+                        #if( $biometrics.get($key).get("FaceImageSource") )
+                        &lt;td&gt; &lt;img src=$biometrics.get($key).get("FaceImageSource") border=0 width=85 height=80 /&gt; &lt;/td&gt;
+                        #end #if( $biometrics.get($key).get("subType") == "applicant" &amp;&amp; $ExceptionImageSource )
+                        &lt;td&gt; &lt;img src=${ExceptionImageSource} border=0 width=85 height=80 /&gt; &lt;/td&gt;
+                        #end
+                    &lt;/tr&gt;
+                &lt;/table&gt;
+            &lt;/table&gt;
+            #end &lt;br /&gt;
+            &lt;hr /&gt; &lt;br /&gt;
+        &lt;/div&gt;
+        &lt;div&gt;
+            &lt;p class="head"&gt;${ImportantGuidelines}&lt;/p&gt;
+            &lt;ol&gt;
+                &lt;li&gt;&lt;span&gt;Your application has been successfully submitted for review.&lt;/span&gt;&lt;/li&gt;
+                &lt;li&gt;&lt;span&gt;All demographics, documents, and biometrics have been received and are under
+                        verification.&lt;/span&gt;&lt;/li&gt;
+                &lt;li&gt;&lt;span&gt;You will receive updates on the progress via SMS/Email.&lt;/span&gt;&lt;/li&gt;
+                &lt;li&gt;&lt;span&gt;Contact support or visit the nearest enrollment center if assistance is required.&lt;/span&gt;&lt;/li&gt;
+            &lt;/ol&gt;
+        &lt;/div&gt;
+&lt;/body&gt;
+&lt;/html&gt;</t>
+  </si>
 </sst>
 </file>
 
@@ -8843,7 +8843,7 @@
         <v>13</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G28">
         <v>10001</v>
@@ -12903,7 +12903,7 @@
         <v>13</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G144">
         <v>10002</v>
@@ -13008,7 +13008,7 @@
         <v>13</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G147">
         <v>10002</v>
@@ -20953,7 +20953,7 @@
         <v>13</v>
       </c>
       <c r="F374" s="4" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="G374">
         <v>10002</v>
@@ -20962,7 +20962,7 @@
         <v>27</v>
       </c>
       <c r="I374" s="5" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="J374" t="s">
         <v>17</v>

--- a/mosip_master/xlsx/template.xlsx
+++ b/mosip_master/xlsx/template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nira-registration\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TF-NIRA-REPOS\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8684C12B-95B2-42BA-AC14-985B73E3E5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8B3F62-A12F-4FA4-B958-1BFB33170FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3388" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3415" uniqueCount="963">
   <si>
     <t>id</t>
   </si>
@@ -7506,6 +7506,33 @@
 &lt;/body&gt;
 &lt;/html&gt;</t>
   </si>
+  <si>
+    <t>Template for technical issue with error Email</t>
+  </si>
+  <si>
+    <t>Template for technical issue with error Subject</t>
+  </si>
+  <si>
+    <t>Template for technical issue with error SMS</t>
+  </si>
+  <si>
+    <t>RPR_TEC_ISSUE_ERROR_EMAIL</t>
+  </si>
+  <si>
+    <t>RPR_TEC_ISSUE_ERROR_EMAIL_SUB</t>
+  </si>
+  <si>
+    <t>RPR_TEC_ISSUE_ERROR_SMS</t>
+  </si>
+  <si>
+    <t>Dear $!surname_eng $!givenName_eng,
+	We regret to inform you that your request for a National Identification Number (NIN) $!MASKEDNIN linked to Registration ID $!RID has encountered an issue - $!FAILURE_REASON.
+	Please restart the registration process by submitting a new application.
+	Thank you for your understanding.</t>
+  </si>
+  <si>
+    <t>Application failed</t>
+  </si>
 </sst>
 </file>
 
@@ -20971,6 +20998,111 @@
         <v>911</v>
       </c>
     </row>
+    <row r="375" spans="1:11" ht="165" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>2007</v>
+      </c>
+      <c r="B375" t="s">
+        <v>955</v>
+      </c>
+      <c r="C375" t="s">
+        <v>955</v>
+      </c>
+      <c r="D375" t="s">
+        <v>12</v>
+      </c>
+      <c r="E375" t="s">
+        <v>13</v>
+      </c>
+      <c r="F375" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="G375">
+        <v>10003</v>
+      </c>
+      <c r="H375" t="s">
+        <v>31</v>
+      </c>
+      <c r="I375" t="s">
+        <v>958</v>
+      </c>
+      <c r="J375" t="s">
+        <v>17</v>
+      </c>
+      <c r="K375" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>2008</v>
+      </c>
+      <c r="B376" t="s">
+        <v>956</v>
+      </c>
+      <c r="C376" t="s">
+        <v>956</v>
+      </c>
+      <c r="D376" t="s">
+        <v>12</v>
+      </c>
+      <c r="E376" t="s">
+        <v>13</v>
+      </c>
+      <c r="F376" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="G376">
+        <v>10003</v>
+      </c>
+      <c r="H376" t="s">
+        <v>31</v>
+      </c>
+      <c r="I376" t="s">
+        <v>959</v>
+      </c>
+      <c r="J376" t="s">
+        <v>17</v>
+      </c>
+      <c r="K376" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="377" spans="1:11" ht="165" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>2009</v>
+      </c>
+      <c r="B377" t="s">
+        <v>957</v>
+      </c>
+      <c r="C377" t="s">
+        <v>957</v>
+      </c>
+      <c r="D377" t="s">
+        <v>12</v>
+      </c>
+      <c r="E377" t="s">
+        <v>13</v>
+      </c>
+      <c r="F377" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="G377">
+        <v>10003</v>
+      </c>
+      <c r="H377" t="s">
+        <v>31</v>
+      </c>
+      <c r="I377" t="s">
+        <v>960</v>
+      </c>
+      <c r="J377" t="s">
+        <v>17</v>
+      </c>
+      <c r="K377" t="s">
+        <v>911</v>
+      </c>
+    </row>
     <row r="622" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F622" s="1"/>
     </row>
